--- a/docs/qms/evidence-2026/00_Overview_and_Map/EM26-00_Evidence_Map_2025_to_2026.xlsx
+++ b/docs/qms/evidence-2026/00_Overview_and_Map/EM26-00_Evidence_Map_2025_to_2026.xlsx
@@ -1090,7 +1090,7 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>15_Testing/Failures/QA-FAIL-2026-01…05</t>
+          <t>15_Testing/Failures/QA-FAIL-2026-01…07</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -1100,7 +1100,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>Five real failures</t>
+          <t>Seven real failures; six closed, one corrective action open</t>
         </is>
       </c>
     </row>
@@ -1122,7 +1122,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>15_Testing/Failures/DEF-2026-01 (REG-04 + GitHub commits)</t>
+          <t>15_Testing/Failures/DEF-2026-01 (REG-04 + GitHub commits + project board)</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1132,7 +1132,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>Board not yet populated</t>
+          <t>Fix commits e0ed4d0, 3feb5db, 5ddf8a6, 736ea61</t>
         </is>
       </c>
     </row>
@@ -1164,7 +1164,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>40/40, 127/127, tsc 0</t>
+          <t>Run 4 on v1.4.1: 50/50, 131/131, tsc 0; acceptance 11/11</t>
         </is>
       </c>
     </row>
@@ -1659,7 +1659,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D57"/>
+  <dimension ref="A1:D59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -2016,7 +2016,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>RECORD — Open</t>
+          <t>RECORD — Closed — effectiveness verified</t>
         </is>
       </c>
     </row>
@@ -2038,7 +2038,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>RECORD — Open</t>
+          <t>RECORD — Closed — effectiveness verified</t>
         </is>
       </c>
     </row>
@@ -2060,7 +2060,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>RECORD — Open</t>
+          <t>RECORD — Closed — effectiveness verified</t>
         </is>
       </c>
     </row>
@@ -2082,112 +2082,112 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>RECORD — Open</t>
+          <t>RECORD — Closed — effectiveness verified</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>DEF-2026-01</t>
+          <t>QA-FAIL-2026-06</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Defect Linking Evidence – DEF-2026-01 (QA-FAIL-2026-01 → NC-2026-010 → fix commits)</t>
+          <t>Failed Functional Test Evidence – QA-FAIL-2026-06: Logout recorded as anonymous after the revocation fix</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>15_Testing/Failures/DEF-2026-01_Defect_Linking_GitHub_REG-04.docx</t>
+          <t>15_Testing/Failures/QA-FAIL-2026-06_Logout_recorded_as_anonymous_after_the_r.docx</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>RECORD</t>
+          <t>RECORD — Closed — effectiveness verified</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>REG-2026-01</t>
+          <t>QA-FAIL-2026-07</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>Regression Testing on Defects – REG-2026-01</t>
+          <t>Failed Functional Test Evidence – QA-FAIL-2026-07: Upload and chat return HTTP 500 after redeploy</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>15_Testing/Failures/REG-2026-01_Regression_Test_Record.docx</t>
+          <t>15_Testing/Failures/QA-FAIL-2026-07_Upload_and_chat_return_HTTP_500_after_re.docx</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>EXECUTED — record</t>
+          <t>RECORD — Open — correction verified</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>EM26-15</t>
+          <t>DEF-2026-01</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Test Failure Documentation and Test Summary – EchoMind Enterprise</t>
+          <t>Defect Linking Evidence – DEF-2026-01 (QA-FAIL-2026-01 → NC-2026-010 → fix commits)</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>15_Testing/EM26-15_Test_Summary_Report.docx</t>
+          <t>15_Testing/Failures/DEF-2026-01_Defect_Linking_GitHub_REG-04.docx</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>DRAFT — not yet approved</t>
+          <t>RECORD</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>EM26-13</t>
+          <t>REG-2026-01</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>Acceptance Criteria Review – EchoMind Enterprise</t>
+          <t>Regression Testing on Defects – REG-2026-01</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>13_Acceptance_Criteria/EM26-13_Acceptance_Criteria_Review.docx</t>
+          <t>15_Testing/Failures/REG-2026-01_Regression_Test_Record.docx</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>DRAFT — not yet approved</t>
+          <t>EXECUTED — record</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>EM26-11</t>
+          <t>EM26-15</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Deliverables Review – EchoMind Enterprise (Feb–Oct 2026)</t>
+          <t>Test Failure Documentation and Test Summary – EchoMind Enterprise</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>11_Deliverables_Review/EM26-11_Deliverables_Review.docx</t>
+          <t>15_Testing/EM26-15_Test_Summary_Report.docx</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -2199,17 +2199,17 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>EM26-12</t>
+          <t>EM26-13</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>Scheduling Review – EchoMind Enterprise (Feb–Oct 2026)</t>
+          <t>Acceptance Criteria Review – EchoMind Enterprise</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>12_Scheduling_Review/EM26-12_Scheduling_Review.docx</t>
+          <t>13_Acceptance_Criteria/EM26-13_Acceptance_Criteria_Review.docx</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -2221,17 +2221,17 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>EM26-14</t>
+          <t>EM26-11</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>External Provider Review – EchoMind Enterprise</t>
+          <t>Deliverables Review – EchoMind Enterprise (Feb–Oct 2026)</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>14_Provider_Review/EM26-14_Provider_Review.docx</t>
+          <t>11_Deliverables_Review/EM26-11_Deliverables_Review.docx</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -2243,17 +2243,17 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>EM26-14b</t>
+          <t>EM26-12</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>Provider Performance Review – EchoMind Enterprise</t>
+          <t>Scheduling Review – EchoMind Enterprise (Feb–Oct 2026)</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>14_Provider_Review/EM26-14b_Provider_Performance_Review.docx</t>
+          <t>12_Scheduling_Review/EM26-12_Scheduling_Review.docx</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -2265,17 +2265,17 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>EM26-16</t>
+          <t>EM26-14</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Lessons Learnt – EchoMind Enterprise (2026)</t>
+          <t>External Provider Review – EchoMind Enterprise</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>16_Lessons_Learnt/EM26-16_Lessons_Learnt.docx</t>
+          <t>14_Provider_Review/EM26-14_Provider_Review.docx</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -2287,17 +2287,17 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>EM26-16b</t>
+          <t>EM26-14b</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>Lessons Learnt Logbook – EchoMind Enterprise (2026)</t>
+          <t>Provider Performance Review – EchoMind Enterprise</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>16_Lessons_Learnt/EM26-16b_Lessons_Learnt_Logbook.docx</t>
+          <t>14_Provider_Review/EM26-14b_Provider_Performance_Review.docx</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -2309,61 +2309,61 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>EM26-02a</t>
+          <t>EM26-16</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Meeting Minutes – Design / Architecture Review (TEMPLATE)</t>
+          <t>Lessons Learnt – EchoMind Enterprise (2026)</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>02_Meeting_Records/EM26-02a_Meeting_Minutes_Template_Design_Architecture_Review.docx</t>
+          <t>16_Lessons_Learnt/EM26-16_Lessons_Learnt.docx</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>TEMPLATE</t>
+          <t>DRAFT — not yet approved</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>EM26-02b</t>
+          <t>EM26-16b</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>Meeting Minutes – External Provider Review (TEMPLATE)</t>
+          <t>Lessons Learnt Logbook – EchoMind Enterprise (2026)</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>02_Meeting_Records/EM26-02b_Meeting_Minutes_Template_External_Provider_Review.docx</t>
+          <t>16_Lessons_Learnt/EM26-16b_Lessons_Learnt_Logbook.docx</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>TEMPLATE</t>
+          <t>DRAFT — not yet approved</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>EM26-02c</t>
+          <t>EM26-02a</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Meeting Minutes – QA / Release Review (TEMPLATE)</t>
+          <t>Meeting Minutes – Design / Architecture Review (TEMPLATE)</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>02_Meeting_Records/EM26-02c_Meeting_Minutes_Template_QA_Release_Review.docx</t>
+          <t>02_Meeting_Records/EM26-02a_Meeting_Minutes_Template_Design_Architecture_Review.docx</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -2375,83 +2375,83 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>EM26-02d</t>
+          <t>EM26-02b</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>Management Review – EchoMind Product Input Pack</t>
+          <t>Meeting Minutes – External Provider Review (TEMPLATE)</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>02_Meeting_Records/EM26-02d_Management_Review_Input_EchoMind.docx</t>
+          <t>02_Meeting_Records/EM26-02b_Meeting_Minutes_Template_External_Provider_Review.docx</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>INPUT PACK</t>
+          <t>TEMPLATE</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>EM26-01</t>
+          <t>EM26-02c</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>EchoMind Enterprise – Privacy, Security &amp; Compliance Overview</t>
+          <t>Meeting Minutes – QA / Release Review (TEMPLATE)</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>01_Privacy_Security/EM26-01_Privacy_Security_Compliance_Overview.docx</t>
+          <t>02_Meeting_Records/EM26-02c_Meeting_Minutes_Template_QA_Release_Review.docx</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>DRAFT — not yet approved</t>
+          <t>TEMPLATE</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>EM26-00</t>
+          <t>EM26-02d</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>EchoMind Enterprise – ISO 9001:2015 Audit Package</t>
+          <t>Management Review – EchoMind Product Input Pack</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>00_Overview_and_Map/EM26-00_ISO9001_Audit_Package_EchoMind_Enterprise.docx</t>
+          <t>02_Meeting_Records/EM26-02d_Management_Review_Input_EchoMind.docx</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>DRAFT — not yet approved</t>
+          <t>INPUT PACK</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>EM26-00b</t>
+          <t>EM26-01</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>Clause 8 Records – EchoMind Enterprise</t>
+          <t>EchoMind Enterprise – Privacy, Security &amp; Compliance Overview</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>00_Overview_and_Map/EM26-00b_Clause8_Records_EchoMind_Enterprise.docx</t>
+          <t>01_Privacy_Security/EM26-01_Privacy_Security_Compliance_Overview.docx</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -2463,61 +2463,61 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>EM26-12</t>
+          <t>EM26-00</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>EM26-12_SDLC_Record.xlsx</t>
+          <t>EchoMind Enterprise – ISO 9001:2015 Audit Package</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>12_Scheduling_Review/EM26-12_SDLC_Record.xlsx</t>
+          <t>00_Overview_and_Map/EM26-00_ISO9001_Audit_Package_EchoMind_Enterprise.docx</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>Workbook</t>
+          <t>DRAFT — not yet approved</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>EM26-16</t>
+          <t>EM26-00b</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>EM26-16_Lessons_Learnt_Log.xlsx</t>
+          <t>Clause 8 Records – EchoMind Enterprise</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>16_Lessons_Learnt/EM26-16_Lessons_Learnt_Log.xlsx</t>
+          <t>00_Overview_and_Map/EM26-00b_Clause8_Records_EchoMind_Enterprise.docx</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>Workbook</t>
+          <t>DRAFT — not yet approved</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>EM26-17</t>
+          <t>EM26-12</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>EM26-17_NFR_Register.xlsx</t>
+          <t>EM26-12_SDLC_Record.xlsx</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>17_NFR_Register/EM26-17_NFR_Register.xlsx</t>
+          <t>12_Scheduling_Review/EM26-12_SDLC_Record.xlsx</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -2529,17 +2529,17 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>EM26-18</t>
+          <t>EM26-16</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>EM26-18_Review_Feedback_Action_Log.xlsx</t>
+          <t>EM26-16_Lessons_Learnt_Log.xlsx</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>18_Review_Actions/EM26-18_Review_Feedback_Action_Log.xlsx</t>
+          <t>16_Lessons_Learnt/EM26-16_Lessons_Learnt_Log.xlsx</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -2551,61 +2551,61 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>SCR-01</t>
+          <t>EM26-17</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>login gate</t>
+          <t>EM26-17_NFR_Register.xlsx</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Screens/SCR-01_login_gate.png</t>
+          <t>17_NFR_Register/EM26-17_NFR_Register.xlsx</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>Screenshot 2026-10-06</t>
+          <t>Workbook</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>SCR-02</t>
+          <t>EM26-18</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>login rejected</t>
+          <t>EM26-18_Review_Feedback_Action_Log.xlsx</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Screens/SCR-02_login_rejected.png</t>
+          <t>18_Review_Actions/EM26-18_Review_Feedback_Action_Log.xlsx</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>Screenshot 2026-10-06</t>
+          <t>Workbook</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>SCR-03</t>
+          <t>SCR-01</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>knowledge chat home</t>
+          <t>login gate</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Screens/SCR-03_knowledge_chat_home.png</t>
+          <t>Screens/SCR-01_login_gate.png</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
@@ -2617,17 +2617,17 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>SCR-04</t>
+          <t>SCR-02</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>grounded answer with citations</t>
+          <t>login rejected</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Screens/SCR-04_grounded_answer_with_citations.png</t>
+          <t>Screens/SCR-02_login_rejected.png</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
@@ -2639,17 +2639,17 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>SCR-05</t>
+          <t>SCR-03</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>live transcript</t>
+          <t>knowledge chat home</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Screens/SCR-05_live_transcript.png</t>
+          <t>Screens/SCR-03_knowledge_chat_home.png</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
@@ -2661,17 +2661,17 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>SCR-06</t>
+          <t>SCR-04</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>voice conversation</t>
+          <t>grounded answer with citations</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Screens/SCR-06_voice_conversation.png</t>
+          <t>Screens/SCR-04_grounded_answer_with_citations.png</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
@@ -2683,17 +2683,17 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>SCR-07</t>
+          <t>SCR-05</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>document studio</t>
+          <t>live transcript</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>Screens/SCR-07_document_studio.png</t>
+          <t>Screens/SCR-05_live_transcript.png</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
@@ -2705,17 +2705,17 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>SCR-08</t>
+          <t>SCR-06</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>settings admin</t>
+          <t>voice conversation</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Screens/SCR-08_settings_admin.png</t>
+          <t>Screens/SCR-06_voice_conversation.png</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
@@ -2727,17 +2727,17 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>SCR-09</t>
+          <t>SCR-07</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>api version</t>
+          <t>document studio</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>Screens/SCR-09_api_version.png</t>
+          <t>Screens/SCR-07_document_studio.png</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
@@ -2749,17 +2749,17 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>SCR-10</t>
+          <t>SCR-08</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>github repository</t>
+          <t>settings admin</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Screens/SCR-10_github_repository.png</t>
+          <t>Screens/SCR-08_settings_admin.png</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
@@ -2771,17 +2771,17 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>SCR-11</t>
+          <t>SCR-09</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>github commit history</t>
+          <t>api version</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>Screens/SCR-11_github_commit_history.png</t>
+          <t>Screens/SCR-09_api_version.png</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
@@ -2793,17 +2793,17 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>SCR-12</t>
+          <t>SCR-10</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>github tag v1.4.0</t>
+          <t>github repository</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>Screens/SCR-12_github_tag_v1.4.0.png</t>
+          <t>Screens/SCR-10_github_repository.png</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
@@ -2815,17 +2815,17 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>SCR-13</t>
+          <t>SCR-11</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>github fix commit 5ddf8a6</t>
+          <t>github commit history</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>Screens/SCR-13_github_fix_commit_5ddf8a6.png</t>
+          <t>Screens/SCR-11_github_commit_history.png</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
@@ -2837,17 +2837,17 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>SCR-14</t>
+          <t>SCR-12</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>github fix commit 4e27109</t>
+          <t>github tag v1.4.0</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>Screens/SCR-14_github_fix_commit_4e27109.png</t>
+          <t>Screens/SCR-12_github_tag_v1.4.0.png</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
@@ -2859,17 +2859,17 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>SCR-15</t>
+          <t>SCR-13</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>test execution log</t>
+          <t>github fix commit 5ddf8a6</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>Screens/SCR-15_test_execution_log.png</t>
+          <t>Screens/SCR-13_github_fix_commit_5ddf8a6.png</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
@@ -2881,17 +2881,17 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>SCR-16</t>
+          <t>SCR-14</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>service stack status</t>
+          <t>github fix commit 4e27109</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>Screens/SCR-16_service_stack_status.png</t>
+          <t>Screens/SCR-14_github_fix_commit_4e27109.png</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
@@ -2903,20 +2903,64 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
+          <t>SCR-15</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>test execution log</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>Screens/SCR-15_test_execution_log.png</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>Screenshot 2026-10-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>SCR-16</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>service stack status</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>Screens/SCR-16_service_stack_status.png</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>Screenshot 2026-10-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
           <t>SCR-17</t>
         </is>
       </c>
-      <c r="B57" s="2" t="inlineStr">
+      <c r="B59" s="2" t="inlineStr">
         <is>
           <t>regression suites</t>
         </is>
       </c>
-      <c r="C57" s="2" t="inlineStr">
+      <c r="C59" s="2" t="inlineStr">
         <is>
           <t>Screens/SCR-17_regression_suites.png</t>
         </is>
       </c>
-      <c r="D57" s="2" t="inlineStr">
+      <c r="D59" s="2" t="inlineStr">
         <is>
           <t>Screenshot 2026-10-06</t>
         </is>

--- a/docs/qms/evidence-2026/00_Overview_and_Map/EM26-00_Evidence_Map_2025_to_2026.xlsx
+++ b/docs/qms/evidence-2026/00_Overview_and_Map/EM26-00_Evidence_Map_2025_to_2026.xlsx
@@ -480,7 +480,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Audit package for the GSU appliance project</t>
+          <t>Audit package for the 2025 university pilot appliance project</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -667,7 +667,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>1. AJACE EchoMind AI LLM Appliance – Privacy, Security &amp; Compliance Overview for Grambling State University.docx</t>
+          <t>1. AJACE EchoMind AI LLM Appliance – Privacy, Security &amp; Compliance Overview for &lt;university pilot customer&gt;.docx</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">

--- a/docs/qms/evidence-2026/00_Overview_and_Map/EM26-00_Evidence_Map_2025_to_2026.xlsx
+++ b/docs/qms/evidence-2026/00_Overview_and_Map/EM26-00_Evidence_Map_2025_to_2026.xlsx
@@ -1659,7 +1659,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D59"/>
+  <dimension ref="A1:D61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -2966,6 +2966,50 @@
         </is>
       </c>
     </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>SCR-18</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>github tag v1.4.1</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>Screens/SCR-18_github_tag_v1.4.1.png</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>Screenshot 2026-10-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>SCR-19</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>github fix commit e0ed4d0</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>Screens/SCR-19_github_fix_commit_e0ed4d0.png</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>Screenshot 2026-10-06</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/qms/evidence-2026/00_Overview_and_Map/EM26-00_Evidence_Map_2025_to_2026.xlsx
+++ b/docs/qms/evidence-2026/00_Overview_and_Map/EM26-00_Evidence_Map_2025_to_2026.xlsx
@@ -1482,17 +1482,17 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>15_Testing test cases + EM26-13; GitHub board (to populate)</t>
+          <t>GitHub issues #4–#68 on the project board + 15_Testing test cases + EM26-13 (SCR-20, SCR-21)</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Created</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>No Jira for the rebuilt product</t>
+          <t>GitHub issues replace Jira for the rebuilt product</t>
         </is>
       </c>
     </row>
@@ -1514,15 +1514,19 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>EM26-12 + SCR-11 commit history; GitHub board (to populate)</t>
+          <t>GitHub project board (SCR-20) + EM26-12 + SCR-11 commit history</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>Partial</t>
-        </is>
-      </c>
-      <c r="F35" s="2" t="inlineStr"/>
+          <t>Created</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>Board created 2026-10-06; earlier work transcribed</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -1638,12 +1642,12 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>GitHub board (to populate)</t>
+          <t>Screens/SCR-20_github_project_board.png</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Created</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr"/>
@@ -1659,7 +1663,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D61"/>
+  <dimension ref="A1:D63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -3010,6 +3014,50 @@
         </is>
       </c>
     </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>SCR-20</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>github project board</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>Screens/SCR-20_github_project_board.png</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>Screenshot 2026-10-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>SCR-21</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>github defect ticket NC-2026-012</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>Screens/SCR-21_github_defect_ticket_NC-2026-012.png</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>Screenshot 2026-10-06</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/qms/evidence-2026/00_Overview_and_Map/EM26-00_Evidence_Map_2025_to_2026.xlsx
+++ b/docs/qms/evidence-2026/00_Overview_and_Map/EM26-00_Evidence_Map_2025_to_2026.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Map 2025 to 2026" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="2026 pack index" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Map 2025 to 2026" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026 pack index" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -724,7 +724,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>From git history; reviewer blank</t>
+          <t>From git history; reviewed and approved 2026-10-07</t>
         </is>
       </c>
     </row>
@@ -912,7 +912,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>Scores PROPOSED — reviewer to confirm</t>
+          <t>Scores confirmed at review, approved 2026-10-07</t>
         </is>
       </c>
     </row>
@@ -1284,7 +1284,7 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>Product-level procedure, DRAFT</t>
+          <t>Product-level procedure, approved 2026-10-07</t>
         </is>
       </c>
     </row>
@@ -2196,7 +2196,7 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>DRAFT — not yet approved</t>
+          <t>APPROVED — 2026-10-07 (AR-2026-001)</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>DRAFT — not yet approved</t>
+          <t>APPROVED — 2026-10-07 (AR-2026-001)</t>
         </is>
       </c>
     </row>
@@ -2240,7 +2240,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>DRAFT — not yet approved</t>
+          <t>APPROVED — 2026-10-07 (AR-2026-001)</t>
         </is>
       </c>
     </row>
@@ -2262,7 +2262,7 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>DRAFT — not yet approved</t>
+          <t>APPROVED — 2026-10-07 (AR-2026-001)</t>
         </is>
       </c>
     </row>
@@ -2284,7 +2284,7 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>DRAFT — not yet approved</t>
+          <t>APPROVED — 2026-10-07 (AR-2026-001)</t>
         </is>
       </c>
     </row>
@@ -2306,7 +2306,7 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>DRAFT — not yet approved</t>
+          <t>APPROVED — 2026-10-07 (AR-2026-001)</t>
         </is>
       </c>
     </row>
@@ -2328,7 +2328,7 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>DRAFT — not yet approved</t>
+          <t>APPROVED — 2026-10-07 (AR-2026-001)</t>
         </is>
       </c>
     </row>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>DRAFT — not yet approved</t>
+          <t>APPROVED — 2026-10-07 (AR-2026-001)</t>
         </is>
       </c>
     </row>
@@ -2460,7 +2460,7 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>DRAFT — not yet approved</t>
+          <t>APPROVED — 2026-10-07 (AR-2026-001)</t>
         </is>
       </c>
     </row>
@@ -2482,7 +2482,7 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>DRAFT — not yet approved</t>
+          <t>APPROVED — 2026-10-07 (AR-2026-001)</t>
         </is>
       </c>
     </row>
@@ -2504,7 +2504,7 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>DRAFT — not yet approved</t>
+          <t>APPROVED — 2026-10-07 (AR-2026-001)</t>
         </is>
       </c>
     </row>

--- a/docs/qms/evidence-2026/00_Overview_and_Map/EM26-00_Evidence_Map_2025_to_2026.xlsx
+++ b/docs/qms/evidence-2026/00_Overview_and_Map/EM26-00_Evidence_Map_2025_to_2026.xlsx
@@ -1196,7 +1196,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>12 lessons, each traced</t>
+          <t>17 lessons, each traced</t>
         </is>
       </c>
     </row>

--- a/docs/qms/evidence-2026/00_Overview_and_Map/EM26-00_Evidence_Map_2025_to_2026.xlsx
+++ b/docs/qms/evidence-2026/00_Overview_and_Map/EM26-00_Evidence_Map_2025_to_2026.xlsx
@@ -2262,7 +2262,7 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>APPROVED — 2026-10-07 (AR-2026-001)</t>
+          <t>APPROVED — rev 1.1 2026-10-10 (AR-2026-002); rev 1.0 2026-10-07 (AR-2026-001)</t>
         </is>
       </c>
     </row>
@@ -2328,7 +2328,7 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>APPROVED — 2026-10-07 (AR-2026-001)</t>
+          <t>APPROVED — rev 1.1 2026-10-10 (AR-2026-002); rev 1.0 2026-10-07 (AR-2026-001)</t>
         </is>
       </c>
     </row>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>APPROVED — 2026-10-07 (AR-2026-001)</t>
+          <t>APPROVED — rev 1.1 2026-10-10 (AR-2026-002); rev 1.0 2026-10-07 (AR-2026-001)</t>
         </is>
       </c>
     </row>
@@ -2482,7 +2482,7 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>APPROVED — 2026-10-07 (AR-2026-001)</t>
+          <t>APPROVED — rev 1.1 2026-10-10 (AR-2026-002); rev 1.0 2026-10-07 (AR-2026-001)</t>
         </is>
       </c>
     </row>

--- a/docs/qms/evidence-2026/00_Overview_and_Map/EM26-00_Evidence_Map_2025_to_2026.xlsx
+++ b/docs/qms/evidence-2026/00_Overview_and_Map/EM26-00_Evidence_Map_2025_to_2026.xlsx
@@ -746,7 +746,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>11_Deliverables_Review/EM26-11 + 18_Review_Actions/EM26-18 workbook</t>
+          <t>11_Deliverables_Review/EM26-11 + 18_Review_Actions/EM26-18 + 19_Excel_Registers/EM26-19</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -754,7 +754,11 @@
           <t>Created</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr"/>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>2025 and 2026 reviews in one log</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -806,7 +810,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>12_Scheduling_Review/EM26-12_SDLC_Record.xlsx</t>
+          <t>12_Scheduling_Review/EM26-12_SDLC_Record.xlsx + 19_Excel_Registers/EM26-22_Product_Roadmap.xlsx</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -816,7 +820,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>Actual phases; future dates left for management</t>
+          <t>2025 plan vs actual; 2026 delivered; forward plan</t>
         </is>
       </c>
     </row>
@@ -1663,7 +1667,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D63"/>
+  <dimension ref="A1:D67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -2599,105 +2603,105 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>SCR-01</t>
+          <t>EM26-19</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>login gate</t>
+          <t>EM26-19_Deliverable_Review_Feedback_and_Action_Log.xlsx</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Screens/SCR-01_login_gate.png</t>
+          <t>19_Excel_Registers/EM26-19_Deliverable_Review_Feedback_and_Action_Log.xlsx</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>Screenshot 2026-10-06</t>
+          <t>Workbook</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>SCR-02</t>
+          <t>EM26-20</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>login rejected</t>
+          <t>EM26-20_Functional_Requirements.xlsx</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Screens/SCR-02_login_rejected.png</t>
+          <t>19_Excel_Registers/EM26-20_Functional_Requirements.xlsx</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>Screenshot 2026-10-06</t>
+          <t>Workbook</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>SCR-03</t>
+          <t>EM26-21</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>knowledge chat home</t>
+          <t>EM26-21_Non_Functional_Requirements.xlsx</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Screens/SCR-03_knowledge_chat_home.png</t>
+          <t>19_Excel_Registers/EM26-21_Non_Functional_Requirements.xlsx</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>Screenshot 2026-10-06</t>
+          <t>Workbook</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>SCR-04</t>
+          <t>EM26-22</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>grounded answer with citations</t>
+          <t>EM26-22_Product_Roadmap.xlsx</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Screens/SCR-04_grounded_answer_with_citations.png</t>
+          <t>19_Excel_Registers/EM26-22_Product_Roadmap.xlsx</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>Screenshot 2026-10-06</t>
+          <t>Workbook</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>SCR-05</t>
+          <t>SCR-01</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>live transcript</t>
+          <t>login gate</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>Screens/SCR-05_live_transcript.png</t>
+          <t>Screens/SCR-01_login_gate.png</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
@@ -2709,17 +2713,17 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>SCR-06</t>
+          <t>SCR-02</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>voice conversation</t>
+          <t>login rejected</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Screens/SCR-06_voice_conversation.png</t>
+          <t>Screens/SCR-02_login_rejected.png</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
@@ -2731,17 +2735,17 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>SCR-07</t>
+          <t>SCR-03</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>document studio</t>
+          <t>knowledge chat home</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>Screens/SCR-07_document_studio.png</t>
+          <t>Screens/SCR-03_knowledge_chat_home.png</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
@@ -2753,17 +2757,17 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>SCR-08</t>
+          <t>SCR-04</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>settings admin</t>
+          <t>grounded answer with citations</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Screens/SCR-08_settings_admin.png</t>
+          <t>Screens/SCR-04_grounded_answer_with_citations.png</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
@@ -2775,17 +2779,17 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>SCR-09</t>
+          <t>SCR-05</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>api version</t>
+          <t>live transcript</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>Screens/SCR-09_api_version.png</t>
+          <t>Screens/SCR-05_live_transcript.png</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
@@ -2797,17 +2801,17 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>SCR-10</t>
+          <t>SCR-06</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>github repository</t>
+          <t>voice conversation</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>Screens/SCR-10_github_repository.png</t>
+          <t>Screens/SCR-06_voice_conversation.png</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
@@ -2819,17 +2823,17 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>SCR-11</t>
+          <t>SCR-07</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>github commit history</t>
+          <t>document studio</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>Screens/SCR-11_github_commit_history.png</t>
+          <t>Screens/SCR-07_document_studio.png</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
@@ -2841,17 +2845,17 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>SCR-12</t>
+          <t>SCR-08</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>github tag v1.4.0</t>
+          <t>settings admin</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>Screens/SCR-12_github_tag_v1.4.0.png</t>
+          <t>Screens/SCR-08_settings_admin.png</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
@@ -2863,17 +2867,17 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>SCR-13</t>
+          <t>SCR-09</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>github fix commit 5ddf8a6</t>
+          <t>api version</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>Screens/SCR-13_github_fix_commit_5ddf8a6.png</t>
+          <t>Screens/SCR-09_api_version.png</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
@@ -2885,17 +2889,17 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>SCR-14</t>
+          <t>SCR-10</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>github fix commit 4e27109</t>
+          <t>github repository</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>Screens/SCR-14_github_fix_commit_4e27109.png</t>
+          <t>Screens/SCR-10_github_repository.png</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
@@ -2907,17 +2911,17 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>SCR-15</t>
+          <t>SCR-11</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>test execution log</t>
+          <t>github commit history</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>Screens/SCR-15_test_execution_log.png</t>
+          <t>Screens/SCR-11_github_commit_history.png</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
@@ -2929,17 +2933,17 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>SCR-16</t>
+          <t>SCR-12</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>service stack status</t>
+          <t>github tag v1.4.0</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>Screens/SCR-16_service_stack_status.png</t>
+          <t>Screens/SCR-12_github_tag_v1.4.0.png</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
@@ -2951,17 +2955,17 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>SCR-17</t>
+          <t>SCR-13</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>regression suites</t>
+          <t>github fix commit 5ddf8a6</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>Screens/SCR-17_regression_suites.png</t>
+          <t>Screens/SCR-13_github_fix_commit_5ddf8a6.png</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
@@ -2973,17 +2977,17 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>SCR-18</t>
+          <t>SCR-14</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>github tag v1.4.1</t>
+          <t>github fix commit 4e27109</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>Screens/SCR-18_github_tag_v1.4.1.png</t>
+          <t>Screens/SCR-14_github_fix_commit_4e27109.png</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
@@ -2995,17 +2999,17 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>SCR-19</t>
+          <t>SCR-15</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>github fix commit e0ed4d0</t>
+          <t>test execution log</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>Screens/SCR-19_github_fix_commit_e0ed4d0.png</t>
+          <t>Screens/SCR-15_test_execution_log.png</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
@@ -3017,17 +3021,17 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>SCR-20</t>
+          <t>SCR-16</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>github project board</t>
+          <t>service stack status</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>Screens/SCR-20_github_project_board.png</t>
+          <t>Screens/SCR-16_service_stack_status.png</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
@@ -3039,20 +3043,108 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
+          <t>SCR-17</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>regression suites</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>Screens/SCR-17_regression_suites.png</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>Screenshot 2026-10-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>SCR-18</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>github tag v1.4.1</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>Screens/SCR-18_github_tag_v1.4.1.png</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>Screenshot 2026-10-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>SCR-19</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>github fix commit e0ed4d0</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>Screens/SCR-19_github_fix_commit_e0ed4d0.png</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>Screenshot 2026-10-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>SCR-20</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>github project board</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>Screens/SCR-20_github_project_board.png</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>Screenshot 2026-10-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
           <t>SCR-21</t>
         </is>
       </c>
-      <c r="B63" s="2" t="inlineStr">
+      <c r="B67" s="2" t="inlineStr">
         <is>
           <t>github defect ticket NC-2026-012</t>
         </is>
       </c>
-      <c r="C63" s="2" t="inlineStr">
+      <c r="C67" s="2" t="inlineStr">
         <is>
           <t>Screens/SCR-21_github_defect_ticket_NC-2026-012.png</t>
         </is>
       </c>
-      <c r="D63" s="2" t="inlineStr">
+      <c r="D67" s="2" t="inlineStr">
         <is>
           <t>Screenshot 2026-10-06</t>
         </is>
